--- a/public/templates/forms/A-150-PhysicalAccessReviewRecords-FORM.xlsx
+++ b/public/templates/forms/A-150-PhysicalAccessReviewRecords-FORM.xlsx
@@ -4,12 +4,15 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -724,14 +727,14 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>« One row per review, not per badge swipe. Each entry records a periodic review of physical-access events, what was found, and what followed. The example rows below show the format: replace them. »</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -768,7 +771,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="50.5" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>LOG-001</t>
@@ -805,7 +808,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="50.5" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>LOG-002</t>
@@ -842,7 +845,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>LOG-003</t>
@@ -992,7 +995,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="66.4" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
           <t>[Reviewed by: e.g., Security coordinator]</t>
@@ -1002,7 +1005,7 @@
       <c r="C29" s="10" t="inlineStr"/>
       <c r="D29" s="10" t="inlineStr"/>
     </row>
-    <row r="30">
+    <row r="30" ht="66.4" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>[Approved by: e.g., Director / Coordinator]</t>
@@ -1112,7 +1115,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="66.4" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Drafter’s note (internal, delete before publishing): Build-order item #35; maintained under the Physical Access Control Policy. Classification Confidential because badge incidents can identify individuals (PII). Reshaped from the generic log into a review record (each row is a periodic review of physical-access events, not one row per badge swipe) and a Source / Event Type column was added. Retention cross-references the Log Retention Schedule; anomalies escalate under the Incident Response Plan. Example rows LOG-001..003 show the format: replace them. Agency-supplied values left in brackets.</t>
@@ -1155,8 +1158,8 @@
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1185,7 +1188,7 @@
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="3" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="34.7" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
         <is>
           <t>How to use: this record holds the dated reviews of physical-access activity: badge data, door events, equipment movement, and badge incidents. Fill the header block on the Log tab, replace every [BRACKETED] field, add one row per review, and delete every « » note before publishing.</t>
@@ -1275,7 +1278,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Source / Event Type</t>
@@ -1297,7 +1300,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Events Reviewed</t>
@@ -1341,7 +1344,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Anomalies / Findings</t>
@@ -1363,7 +1366,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Action Taken / Follow-up</t>
@@ -1467,7 +1470,7 @@
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>